--- a/artfynd/A 20224-2025 artfynd.xlsx
+++ b/artfynd/A 20224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,118 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124947283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Askersund ONO 1160 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6509405</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20224-2025 artfynd.xlsx
+++ b/artfynd/A 20224-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>124947283</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20224-2025 artfynd.xlsx
+++ b/artfynd/A 20224-2025 artfynd.xlsx
@@ -892,11 +892,6 @@
       <c r="B4" t="n">
         <v>95873</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LC</t>
